--- a/Programmazione trimestrale - Periodo 01_2026.xlsx
+++ b/Programmazione trimestrale - Periodo 01_2026.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xx\Documents\TUNDIS\06 - Rosana_2026\A.I.O\SITIO WEB\ITALIANO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337FBCF2-0E06-465C-876E-3BBBB18E8F5E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD35FCA-63D8-4EC1-A0DC-51BE299A1E95}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B046234C-1F0E-4D23-A1FF-F9DC623507B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Turno Mattutino" sheetId="1" r:id="rId1"/>
     <sheet name="Turno Pomeridiano" sheetId="2" r:id="rId2"/>
-    <sheet name="Turno Serale" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
   <si>
     <t>A1: Lunedì e Giovedì (09:00 - 11:00)</t>
   </si>
@@ -47,19 +46,10 @@
     <t>Partecipanti:</t>
   </si>
   <si>
-    <t>A2: Martedì e Giovedì (13:30 - 15:30)</t>
-  </si>
-  <si>
     <t>B1: Lunedì e Venerdì (13:30 - 15:30)</t>
   </si>
   <si>
-    <t>A1: Martedì e Giovedì (19:00 - 21:00)</t>
-  </si>
-  <si>
     <t>Programmazione Corsi - Turno mattutino: Periodo 01_2026</t>
-  </si>
-  <si>
-    <t>Programmazione Corsi serali: Periodo 01_2026</t>
   </si>
   <si>
     <t>Programmazione Corsi - Turno pomeridiano: Periodo 01_2026</t>
@@ -67,12 +57,15 @@
   <si>
     <t>El numero di partecipanti verrà aggiornato.</t>
   </si>
+  <si>
+    <t>A1: Martedì e Giovedì (13:30 - 15:30)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,14 +113,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -161,7 +146,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -188,21 +173,6 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -306,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -314,50 +284,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -365,7 +336,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -374,10 +345,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -704,7 +671,7 @@
     <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="22" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
@@ -1385,14 +1352,14 @@
       <c r="F45" s="4"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="28" t="s">
-        <v>10</v>
+      <c r="B47" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1421,7 +1388,7 @@
     <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="25" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2" s="26"/>
       <c r="D2" s="27"/>
@@ -1429,10 +1396,10 @@
     <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="18" t="s">
         <v>4</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1888,11 +1855,11 @@
       <c r="D45" s="4"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B47" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" s="28" t="s">
-        <v>10</v>
+      <c r="B47" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1903,302 +1870,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16E60DBD-0852-4D00-8782-40DB679F4161}">
-  <dimension ref="A1:B47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="34.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:2" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="17"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>1</v>
-      </c>
-      <c r="B7" s="5">
-        <v>46205</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>2</v>
-      </c>
-      <c r="B8" s="5">
-        <v>46210</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>3</v>
-      </c>
-      <c r="B9" s="5">
-        <v>46217</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>4</v>
-      </c>
-      <c r="B10" s="5">
-        <v>46219</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>5</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46224</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>6</v>
-      </c>
-      <c r="B12" s="5">
-        <v>46226</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>7</v>
-      </c>
-      <c r="B13" s="5">
-        <v>46231</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6">
-        <v>46233</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>9</v>
-      </c>
-      <c r="B15" s="5">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>10</v>
-      </c>
-      <c r="B16" s="5">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>11</v>
-      </c>
-      <c r="B17" s="5">
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>12</v>
-      </c>
-      <c r="B18" s="5">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>13</v>
-      </c>
-      <c r="B19" s="5">
-        <v>46252</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>14</v>
-      </c>
-      <c r="B20" s="5">
-        <v>46254</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>15</v>
-      </c>
-      <c r="B21" s="5">
-        <v>46259</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>16</v>
-      </c>
-      <c r="B22" s="6">
-        <v>46261</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>17</v>
-      </c>
-      <c r="B23" s="5">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>18</v>
-      </c>
-      <c r="B24" s="5">
-        <v>46268</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>19</v>
-      </c>
-      <c r="B25" s="5">
-        <v>46273</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>20</v>
-      </c>
-      <c r="B26" s="5">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>21</v>
-      </c>
-      <c r="B27" s="5">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>22</v>
-      </c>
-      <c r="B28" s="5">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>23</v>
-      </c>
-      <c r="B29" s="5">
-        <v>46287</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>24</v>
-      </c>
-      <c r="B30" s="5">
-        <v>46289</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="3"/>
-    </row>
-    <row r="32" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="4"/>
-    </row>
-    <row r="34" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <v>1</v>
-      </c>
-      <c r="B37" s="3"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
-        <v>2</v>
-      </c>
-      <c r="B38" s="3"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
-        <v>3</v>
-      </c>
-      <c r="B39" s="3"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
-        <v>4</v>
-      </c>
-      <c r="B40" s="3"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
-        <v>5</v>
-      </c>
-      <c r="B41" s="3"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
-        <v>6</v>
-      </c>
-      <c r="B42" s="3"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
-        <v>7</v>
-      </c>
-      <c r="B43" s="3"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
-        <v>8</v>
-      </c>
-      <c r="B44" s="3"/>
-    </row>
-    <row r="45" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="4"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B47" s="28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B4:B5"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>